--- a/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. La lumière est douce. Claire est dans la chambre. Maman prend le pyjama. Le pyjama est doux. Claire met le pyjama. Papa ouvre le lit. La couverture est chaude. Claire se couche. Papa dit : c'est l'heure du dodo. Le corps a besoin de dormir. Claire écoute une petite histoire. Ses yeux se ferment. Maman dit : bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.</t>
+          <t>Le soir arrive. La lumière est douce. Claire est dans la chambre. Maman prend le pyjama. Le pyjama est doux. Claire met le pyjama. Papa ouvre le lit. La couverture est chaude. Claire se couche. C'est l'heure du dodo. Le corps a besoin de dormir. Claire écoute une petite histoire. Ses yeux se ferment. Bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir arrive. La lumière est douce. Claire est dans la chambre. Maman prend le pyjama. Le pyjama est doux. Claire met le pyjama. Papa ouvre le lit. La couverture est chaude. Claire se couche.
+papa|C'est l'heure du dodo.
+narrateur|Le corps a besoin de dormir. Claire écoute une petite histoire. Ses yeux se ferment.
+maman|Bon dodo.
+narrateur|Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, que met Claire ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Claire a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman étaient là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La chambre est calme. Claire dort.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Le soir, que met Claire ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Claire a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman étaient là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|La chambre est calme. Claire dort.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claire met le pyjama</t>
+          <t>La vague bleue de Nina</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La couverture bleue est pliée en vague. Nina met le pyjama. Papa raconte la vague. Nina boit une gorgée. Elle s'endort. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. La lumière est douce. Claire est dans la chambre. Maman prend le pyjama. Le pyjama est doux. Claire met le pyjama. Papa ouvre le lit. La couverture est chaude. Claire se couche. C'est l'heure du dodo. Le corps a besoin de dormir. Claire écoute une petite histoire. Ses yeux se ferment. Bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.</t>
+          <t>La couverture bleue est pliée en vague. Un verre d'eau attend sur la table. Les volets sont à moitié fermés. Un filet d'air sent la nuit. La lumière est douce. Une pantoufle est sous le lit. Nina vit ici, avec papa et maman. En ce moment, Nina est dans la chambre. Nina, le pyjama t'attend. Il est où, maman ? Sur la vague bleue. Maman prend le pyjama. Le pyjama est doux. Il est chaud. Mets le pyjama, Nina. Nina met le pyjama. Les manches glissent. Bravo, Nina. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. La vague bleue s'étale. Nina se couche. C'est l'heure du dodo. Le verre d'eau est là. Oui. Il attend. Le corps a besoin de dormir. Nina écoute une petite histoire. Papa raconte une vague lente. La vague va, puis revient. Comme la couverture. Oui. Comme la couverture. Ses yeux se ferment. Bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Bravo, Nina. Tu as fait du bon travail. Nina respire lentement. Papa reste un moment. Nina s'endort. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1329,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir arrive. La lumière est douce. Claire est dans la chambre. Maman prend le pyjama. Le pyjama est doux. Claire met le pyjama. Papa ouvre le lit. La couverture est chaude. Claire se couche.
+          <t>narrateur|La couverture bleue est pliée en vague.
+narrateur|Un verre d'eau attend sur la table.
+narrateur|Les volets sont à moitié fermés.
+narrateur|Un filet d'air sent la nuit.
+narrateur|La lumière est douce.
+narrateur|Une pantoufle est sous le lit.
+narrateur|Nina vit ici, avec papa et maman.
+narrateur|En ce moment, Nina est dans la chambre.
+maman|Nina, le pyjama t'attend.
+enfant-f|Il est où, maman ?
+maman|Sur la vague bleue.
+narrateur|Maman prend le pyjama.
+narrateur|Le pyjama est doux.
+enfant-f|Il est chaud.
+maman|Mets le pyjama, Nina.
+narrateur|Nina met le pyjama.
+narrateur|Les manches glissent.
+maman|Bravo, Nina.
+maman|Tu as mis le pyjama.
+papa|J'ouvre le lit.
+narrateur|Papa ouvre le lit.
+narrateur|La couverture est chaude.
+narrateur|La vague bleue s'étale.
+narrateur|Nina se couche.
 papa|C'est l'heure du dodo.
-narrateur|Le corps a besoin de dormir. Claire écoute une petite histoire. Ses yeux se ferment.
+enfant-f|Le verre d'eau est là.
+papa|Oui. Il attend.
+narrateur|Le corps a besoin de dormir.
+narrateur|Nina écoute une petite histoire.
+narrateur|Papa raconte une vague lente.
+narrateur|La vague va, puis revient.
+enfant-f|Comme la couverture.
+papa|Oui. Comme la couverture.
+narrateur|Ses yeux se ferment.
 maman|Bon dodo.
-narrateur|Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.</t>
+maman|Le soir, on met le pyjama.
+maman|Puis on va au dodo.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina respire lentement.
+narrateur|Papa reste un moment.
+narrateur|Nina s'endort.
+narrateur|C'est le soir.
+narrateur|C'est le dodo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le soir, que met Claire ?</t>
+          <t>Le soir, que met Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1560,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, que met Claire ?</t>
+          <t>narrateur|Le soir, que met Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Claire a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman étaient là.</t>
+          <t>Nina a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama ? Oui, maman. Bravo, Nina. Le soir, c'est le dodo. La vague bleue est bien à plat.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1732,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Claire a mis le pyjama. Elle s'est couchée. Le soir, c'est le dodo. Papa et maman étaient là.</t>
+          <t>narrateur|Nina a mis le pyjama.
+narrateur|Elle s'est couchée.
+maman|Tu as mis le pyjama ?
+enfant-f|Oui, maman.
+maman|Bravo, Nina.
+papa|Le soir, c'est le dodo.
+narrateur|La vague bleue est bien à plat.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La chambre est calme. Claire dort.</t>
+          <t>Tu veux une gorgée d'eau ? Oui. Une petite. Nina boit une gorgée. L'eau est fraîche. La chambre est calme. Tu es bien au lit ? Oui. Nina dort. Le filet d'air sent encore la nuit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1902,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La chambre est calme. Claire dort.</t>
+          <t>papa|Tu veux une gorgée d'eau ?
+enfant-f|Oui. Une petite.
+narrateur|Nina boit une gorgée.
+narrateur|L'eau est fraîche.
+narrateur|La chambre est calme.
+maman|Tu es bien au lit ?
+enfant-f|Oui.
+narrateur|Nina dort.
+narrateur|Le filet d'air sent encore la nuit.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1938,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. La vague bleue repose. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2078,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai mis le pyjama.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La vague bleue repose.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La couverture bleue est pliée en vague. Un verre d'eau attend sur la table. Les volets sont à moitié fermés. Un filet d'air sent la nuit. La lumière est douce. Une pantoufle est sous le lit. Nina vit ici, avec papa et maman. En ce moment, Nina est dans la chambre. Nina, le pyjama t'attend. Il est où, maman ? Sur la vague bleue. Maman prend le pyjama. Le pyjama est doux. Il est chaud. Mets le pyjama, Nina. Nina met le pyjama. Les manches glissent. Bravo, Nina. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. La vague bleue s'étale. Nina se couche. C'est l'heure du dodo. Le verre d'eau est là. Oui. Il attend. Le corps a besoin de dormir. Nina écoute une petite histoire. Papa raconte une vague lente. La vague va, puis revient. Comme la couverture. Oui. Comme la couverture. Ses yeux se ferment. Bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Bravo, Nina. Tu as fait du bon travail. Nina respire lentement. Papa reste un moment. Nina s'endort. C'est le soir. C'est le dodo.</t>
+          <t>La couverture bleue est pliée en vague. Un pli brille, tout long. Un verre d'eau attend sur la table. Une bulle reste collée au bord. Les volets sont à moitié fermés. Un filet d'air sent la nuit. Il est frais, tout mince. La lumière est douce. Une pantoufle est sous le lit. L'autre pantoufle la cherche. Un oiseau de nuit chante, tout loin. Nina vit ici, avec papa et maman. En ce moment, Nina est dans la chambre. Nina, le pyjama t'attend. Il est où, maman ? Sur la vague bleue. Maman prend le pyjama. Le pyjama est doux. Il est chaud. Mets le pyjama, Nina. Nina met le pyjama. Les manches glissent. Le tissu est un peu frais, puis chaud. Il se réchauffe. Oui. Avec toi. Bravo, Nina. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. La vague bleue s'étale. Nina se couche. C'est l'heure du dodo. Le verre d'eau est là. Oui. Il attend. Le corps a besoin de dormir. Nina écoute une petite histoire. Papa raconte une vague lente. La vague va, puis revient. Elle pose une dentelle d'écume. Comme la couverture. Oui. Comme la couverture. Tout doux. Nina écoute encore. Ses yeux se ferment. Bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Bravo, Nina. Nina respire lentement. Papa reste un moment. Nina s'endort. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt; arrive. La lumière est douce. Claire est dans la chambre. Maman prend le pyjama. Le pyjama est doux. Claire met le pyjama. Papa ouvre le lit. La couverture est chaude. Claire se couche. Papa dit : c'est l'heure du dodo. Le corps a besoin de dormir. Claire écoute une petite histoire. Ses yeux se ferment. Maman dit : bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Claire respire lentement. Papa reste un moment. Claire s'endort.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La couverture bleue est pliée en vague. Un pli brille, tout long. Un verre d'eau attend sur la table. Une bulle reste collée au bord. Les volets sont à moitié fermés. Un filet d'air sent la nuit. Il est frais, tout mince. La lumière est douce. Une pantoufle est sous le lit. L'autre pantoufle la cherche. Un oiseau de nuit chante, tout loin. Nina vit ici, avec papa et maman. En ce moment, Nina est dans la chambre. Nina, le pyjama t'attend. Il est où, maman ? Sur la vague bleue. Maman prend le pyjama. Le pyjama est doux. Il est chaud. Mets le pyjama, Nina. Nina met le pyjama. Les manches glissent. Le tissu est un peu frais, puis chaud. Il se réchauffe. Oui. Avec toi. Bravo, Nina. Tu as mis le pyjama. J'ouvre le lit. Papa ouvre le lit. La couverture est chaude. La vague bleue s'étale. Nina se couche. C'est l'heure du dodo. Le verre d'eau est là. Oui. Il attend. Le corps a besoin de dormir. Nina écoute une petite histoire. Papa raconte une vague lente. La vague va, puis revient. Elle pose une dentelle d'écume. Comme la couverture. Oui. Comme la couverture. Tout doux. Nina écoute encore. Ses yeux se ferment. Bon dodo. Le soir, on met le pyjama. Puis on va au dodo. Bravo, Nina. Nina respire lentement. Papa reste un moment. Nina s'endort. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1330,11 +1330,16 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|La couverture bleue est pliée en vague.
+narrateur|Un pli brille, tout long.
 narrateur|Un verre d'eau attend sur la table.
+narrateur|Une bulle reste collée au bord.
 narrateur|Les volets sont à moitié fermés.
 narrateur|Un filet d'air sent la nuit.
+narrateur|Il est frais, tout mince.
 narrateur|La lumière est douce.
 narrateur|Une pantoufle est sous le lit.
+narrateur|L'autre pantoufle la cherche.
+narrateur|Un oiseau de nuit chante, tout loin.
 narrateur|Nina vit ici, avec papa et maman.
 narrateur|En ce moment, Nina est dans la chambre.
 maman|Nina, le pyjama t'attend.
@@ -1346,6 +1351,9 @@
 maman|Mets le pyjama, Nina.
 narrateur|Nina met le pyjama.
 narrateur|Les manches glissent.
+narrateur|Le tissu est un peu frais, puis chaud.
+enfant-f|Il se réchauffe.
+maman|Oui. Avec toi.
 maman|Bravo, Nina.
 maman|Tu as mis le pyjama.
 papa|J'ouvre le lit.
@@ -1360,14 +1368,16 @@
 narrateur|Nina écoute une petite histoire.
 narrateur|Papa raconte une vague lente.
 narrateur|La vague va, puis revient.
+narrateur|Elle pose une dentelle d'écume.
 enfant-f|Comme la couverture.
 papa|Oui. Comme la couverture.
+papa|Tout doux.
+narrateur|Nina écoute encore.
 narrateur|Ses yeux se ferment.
 maman|Bon dodo.
 maman|Le soir, on met le pyjama.
 maman|Puis on va au dodo.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
 narrateur|Nina respire lentement.
 narrateur|Papa reste un moment.
 narrateur|Nina s'endort.
@@ -1375,7 +1385,6 @@
 narrateur|C'est le dodo.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1405,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, que met Claire ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir, que met Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1563,7 +1572,6 @@
           <t>narrateur|Le soir, que met Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1588,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama ? Oui, maman. Bravo, Nina. Le soir, c'est le dodo. La vague bleue est bien à plat.</t>
+          <t>Nina a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama ? Oui, maman. Bravo, Nina. Le soir, c'est le dodo. La vague bleue est bien à plat. Le verre d'eau brille un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Claire a mis le pyjama. Elle s'est couchée. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo. Papa et maman étaient là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a mis le pyjama. Elle s'est couchée. Tu as mis le pyjama ? Oui, maman. Bravo, Nina. Le soir, c'est le dodo. La vague bleue est bien à plat. Le verre d'eau brille un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,10 +1746,10 @@
 enfant-f|Oui, maman.
 maman|Bravo, Nina.
 papa|Le soir, c'est le dodo.
-narrateur|La vague bleue est bien à plat.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|La vague bleue est bien à plat.
+narrateur|Le verre d'eau brille un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1766,12 +1774,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tu veux une gorgée d'eau ? Oui. Une petite. Nina boit une gorgée. L'eau est fraîche. La chambre est calme. Tu es bien au lit ? Oui. Nina dort. Le filet d'air sent encore la nuit.</t>
+          <t>Tu veux une gorgée d'eau ? Oui. Une petite. Nina boit une gorgée. L'eau est fraîche. La chambre est calme. Tu es bien au lit ? Oui. Nina dort. Le filet d'air sent encore la nuit. Le verre a encore une petite bulle. Je reste un moment. La vague bleue est bien à plat.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La chambre est calme. Claire dort.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu veux une gorgée d'eau ? Oui. Une petite. Nina boit une gorgée. L'eau est fraîche. La chambre est calme. Tu es bien au lit ? Oui. Nina dort. Le filet d'air sent encore la nuit. Le verre a encore une petite bulle. Je reste un moment. La vague bleue est bien à plat.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1910,10 +1918,12 @@
 maman|Tu es bien au lit ?
 enfant-f|Oui.
 narrateur|Nina dort.
-narrateur|Le filet d'air sent encore la nuit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Le filet d'air sent encore la nuit.
+narrateur|Le verre a encore une petite bulle.
+papa|Je reste un moment.
+maman|La vague bleue est bien à plat.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1938,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. La vague bleue repose. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. La vague bleue repose.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. Bravo. La vague bleue repose.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2080,12 +2090,9 @@
         <is>
           <t>enfant-f|J'ai mis le pyjama.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|La vague bleue repose.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La vague bleue repose.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2104,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-10.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Claire, papa, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
